--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484375_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484375_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9081</v>
+        <v>3.1269</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6283</v>
+        <v>1.7382</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2798</v>
+        <v>1.3888</v>
       </c>
       <c r="G2" t="n">
         <v>-1.2064</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7042</v>
+        <v>0.9231</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3098</v>
+        <v>0.4197</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3944</v>
+        <v>0.5034</v>
       </c>
       <c r="V2" t="n">
         <v>2.8242</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.438</v>
+        <v>1.884</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3234</v>
+        <v>2.8783</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8854</v>
+        <v>-0.9943</v>
       </c>
       <c r="G3" t="n">
         <v>3.3328</v>
@@ -688,13 +688,13 @@
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0857</v>
+        <v>0.5317</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5752</v>
+        <v>0.1301</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5105</v>
+        <v>0.4015</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2224</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4109</v>
+        <v>0.0562</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1161</v>
+        <v>0.5003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.527</v>
+        <v>-0.4441</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.2575</v>
+        <v>2.1453</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1765</v>
+        <v>-0.6465</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0809</v>
+        <v>2.7917</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2939</v>
+        <v>3.7928</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3482</v>
+        <v>0.596</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0543</v>
+        <v>3.1968</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9636</v>
+        <v>-1.6476</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8283</v>
+        <v>-1.2425</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1352</v>
+        <v>-0.4051</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7814</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q4" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.3859</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.3624</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.0235</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="W4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>0.7814</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.0689</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.7092000000000001</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.1089</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.1089</v>
-      </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2407</v>
+        <v>0.0318</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3462</v>
+        <v>0.9728</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5869</v>
+        <v>-0.9409</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4729</v>
@@ -844,13 +844,13 @@
         <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0766</v>
+        <v>0.196</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8941</v>
+        <v>-0.2674</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8175</v>
+        <v>0.4634</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2772</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5044</v>
+        <v>-0.0577</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0759</v>
+        <v>-0.2578</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5803</v>
+        <v>0.2002</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1453</v>
+        <v>-2.2575</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6465</v>
+        <v>-2.1765</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7917</v>
+        <v>-0.0809</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7928</v>
+        <v>-1.2939</v>
       </c>
       <c r="K6" t="n">
-        <v>0.596</v>
+        <v>-1.3482</v>
       </c>
       <c r="L6" t="n">
-        <v>3.1968</v>
+        <v>0.0543</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6476</v>
+        <v>-0.9636</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2425</v>
+        <v>-0.8283</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4051</v>
+        <v>-0.1352</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9465</v>
+        <v>0.3095</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.0728</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1597</v>
+        <v>0.3823</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0549</v>
+        <v>1.1089</v>
       </c>
       <c r="W6" t="n">
+        <v>1.1089</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.0549</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7723</v>
+        <v>-0.1009</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7678</v>
+        <v>3.5266</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0045</v>
+        <v>-3.6274</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4889</v>
+        <v>2.9284</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9877</v>
+        <v>1.471</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4988</v>
+        <v>1.4574</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2378</v>
+        <v>4.4411</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1433</v>
+        <v>2.5787</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0945</v>
+        <v>1.8624</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7267</v>
+        <v>-1.5127</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.131</v>
+        <v>-1.1077</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4043</v>
+        <v>-0.4051</v>
       </c>
       <c r="P7" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4788</v>
+        <v>-0.1231</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8335</v>
+        <v>-0.1602</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3548</v>
+        <v>0.037</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-3.1014</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2224</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-3.3238</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8031</v>
+        <v>-0.2422</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9605</v>
+        <v>2.5788</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.7636</v>
+        <v>-2.821</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9284</v>
+        <v>-0.2817</v>
       </c>
       <c r="H8" t="n">
-        <v>1.471</v>
+        <v>-0.1747</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4574</v>
+        <v>-0.107</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4411</v>
+        <v>1.5149</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5787</v>
+        <v>2.0261</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8624</v>
+        <v>-0.5112</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5127</v>
+        <v>-1.7966</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1077</v>
+        <v>-2.2008</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4051</v>
+        <v>0.4043</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8254</v>
+        <v>0.1176</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.1464</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.264</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.1014</v>
+        <v>-0.6642</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2224</v>
+        <v>2.3824</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.3238</v>
+        <v>-3.0466</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0807</v>
+        <v>-0.3479</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0127</v>
+        <v>-0.3434</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0934</v>
+        <v>-0.0045</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2817</v>
+        <v>-0.4889</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1747</v>
+        <v>-1.9877</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.107</v>
+        <v>1.4988</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5149</v>
+        <v>1.2378</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0261</v>
+        <v>0.1433</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5112</v>
+        <v>1.0945</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7966</v>
+        <v>-1.7267</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.2008</v>
+        <v>-2.131</v>
       </c>
       <c r="O9" t="n">
         <v>0.4043</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7208</v>
+        <v>-0.0544</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7125</v>
+        <v>-0.4092</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0083</v>
+        <v>0.3548</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.3824</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.0466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.817</v>
+        <v>-1.7953</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9321</v>
+        <v>-1.0738</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8849</v>
+        <v>-0.7215</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9416</v>
@@ -1234,13 +1234,13 @@
         <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4028</v>
+        <v>-0.3811</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0522</v>
+        <v>-0.1939</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3506</v>
+        <v>-0.1872</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2772</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1174</v>
+        <v>-3.2258</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4099</v>
+        <v>-2.4911</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7075</v>
+        <v>-0.7347</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2686</v>
@@ -1312,13 +1312,13 @@
         <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1167</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0522</v>
+        <v>-0.1334</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1688</v>
+        <v>0.1416</v>
       </c>
       <c r="V11" t="n">
         <v>2.16</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5786</v>
+        <v>-0.6709000000000009</v>
       </c>
       <c r="E12" t="n">
-        <v>7.1211</v>
+        <v>8.028900000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.699699999999998</v>
+        <v>-8.699400000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.488900000000001</v>
+        <v>0.4889000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>-13.6761</v>
@@ -1378,7 +1378,7 @@
         <v>-16.1933</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.004000000000000048</v>
+        <v>-0.004000000000000103</v>
       </c>
       <c r="P12" t="n">
         <v>-3.907</v>
@@ -1390,13 +1390,13 @@
         <v>12.6975</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2337000000000005</v>
+        <v>1.1416</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.1037</v>
+        <v>-1.1959</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3375</v>
+        <v>2.3373</v>
       </c>
       <c r="V12" t="n">
         <v>1.6056</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1607</v>
+        <v>5.4219</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1568</v>
+        <v>4.0569</v>
       </c>
       <c r="F13" t="n">
-        <v>0.004</v>
+        <v>1.365</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7967</v>
+        <v>2.0677</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9688</v>
+        <v>0.1926</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1721</v>
+        <v>1.875</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9699</v>
+        <v>2.213</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8485</v>
+        <v>-0.2021</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1214</v>
+        <v>2.4151</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.1733</v>
+        <v>-0.1453</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1203</v>
+        <v>0.3948</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.2935</v>
+        <v>-0.5401</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2506</v>
+        <v>-0.3137</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9096</v>
+        <v>-0.2613</v>
       </c>
       <c r="U13" t="n">
-        <v>0.341</v>
+        <v>-0.0524</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9414</v>
+        <v>2.1052</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2772</v>
+        <v>2.1052</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.963</v>
+        <v>3.3717</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6524</v>
+        <v>3.6401</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3106</v>
+        <v>-0.2684</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0677</v>
+        <v>0.7967</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1926</v>
+        <v>2.9688</v>
       </c>
       <c r="I14" t="n">
-        <v>1.875</v>
+        <v>-2.1721</v>
       </c>
       <c r="J14" t="n">
-        <v>2.213</v>
+        <v>2.9699</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2021</v>
+        <v>2.8485</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4151</v>
+        <v>0.1214</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1453</v>
+        <v>-2.1733</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3948</v>
+        <v>0.1203</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5401</v>
+        <v>-2.2935</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7726</v>
+        <v>0.4615</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6657</v>
+        <v>0.3929</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1069</v>
+        <v>0.0687</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1052</v>
+        <v>0.9414</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1052</v>
+        <v>0.2772</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PLANELL IGLESIAS</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6514</v>
+        <v>1.2639</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.9604</v>
+        <v>2.1526</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6118</v>
+        <v>-0.8887</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4768</v>
+        <v>1.1689</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0703</v>
+        <v>2.8821</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5936</v>
+        <v>-1.7132</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3521</v>
+        <v>3.5517</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9452</v>
+        <v>3.6454</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1247</v>
+        <v>-2.3828</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1251</v>
+        <v>-0.7634</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0004</v>
+        <v>-1.6194</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
         <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>0.542</v>
+        <v>0.095</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0083</v>
+        <v>-0.6643</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5336</v>
+        <v>0.7592</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5224</v>
+        <v>0.8797</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5459</v>
+        <v>3.2127</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0236</v>
+        <v>-2.333</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1689</v>
+        <v>-1.4054</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8821</v>
+        <v>2.3848</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7132</v>
+        <v>-3.7902</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5517</v>
+        <v>2.4661</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6454</v>
+        <v>3.153</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.6869</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3828</v>
+        <v>-3.8714</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7634</v>
+        <v>-0.7682</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6194</v>
+        <v>-3.1032</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1702,28 +1702,28 @@
         <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6466</v>
+        <v>-0.207</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.271</v>
+        <v>-0.6237</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6244</v>
+        <v>0.4167</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.4921</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>3.3238</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2822</v>
+        <v>0.3993</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5049</v>
+        <v>0.797</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2227</v>
+        <v>-0.3977</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4054</v>
+        <v>0.1063</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3848</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.7902</v>
+        <v>-0.634</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4661</v>
+        <v>0.7158</v>
       </c>
       <c r="K17" t="n">
-        <v>3.153</v>
+        <v>0.6754</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6869</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.8714</v>
+        <v>-0.6095</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7682</v>
+        <v>0.065</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.1032</v>
+        <v>-0.6745</v>
       </c>
       <c r="P17" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8045</v>
+        <v>-0.0977</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3315</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.527</v>
+        <v>-0.1789</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4921</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3238</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. PLANELL IGLESIAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1426</v>
+        <v>0.313</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5948</v>
+        <v>-2.1626</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4522</v>
+        <v>2.4756</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1063</v>
+        <v>0.4768</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7403999999999999</v>
+        <v>1.0703</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.634</v>
+        <v>-0.5936</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7158</v>
+        <v>0.3521</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6754</v>
+        <v>0.9452</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0405</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6095</v>
+        <v>0.1247</v>
       </c>
       <c r="N18" t="n">
-        <v>0.065</v>
+        <v>0.1251</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6745</v>
+        <v>-0.0004</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3544</v>
+        <v>0.2036</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.121</v>
+        <v>-0.1939</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2333</v>
+        <v>0.3975</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0539</v>
+        <v>0.0979</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0796</v>
+        <v>-0.2818</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0257</v>
+        <v>0.3797</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6825</v>
@@ -1936,13 +1936,13 @@
         <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1839</v>
+        <v>0.3357</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1983</v>
+        <v>-0.004</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0144</v>
+        <v>0.3397</v>
       </c>
       <c r="V19" t="n">
         <v>0.4448</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7964</v>
+        <v>-1.2752</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0435</v>
+        <v>-0.7401</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7529</v>
+        <v>-0.5351</v>
       </c>
       <c r="G20" t="n">
         <v>0.4818</v>
@@ -2014,13 +2014,13 @@
         <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6223</v>
+        <v>-0.1011</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4842</v>
+        <v>-0.1808</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1382</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4373</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9471</v>
+        <v>-2.2877</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1441</v>
+        <v>0.5974</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8031</v>
+        <v>-2.8851</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6804</v>
+        <v>-0.7375</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1678</v>
+        <v>1.2461</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8482</v>
+        <v>-1.9836</v>
       </c>
       <c r="J21" t="n">
-        <v>1.088</v>
+        <v>2.0499</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7217</v>
+        <v>2.0095</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7684</v>
+        <v>-2.7874</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5538</v>
+        <v>-0.7634</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2146</v>
+        <v>-2.0241</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1435</v>
+        <v>-0.1678</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4404</v>
+        <v>-0.4758</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.308</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2149</v>
+        <v>-1.7731</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.719</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5315</v>
+        <v>-2.563</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5974</v>
+        <v>-1.6496</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1289</v>
+        <v>-0.9134</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7375</v>
+        <v>-0.6804</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2461</v>
+        <v>1.1678</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9836</v>
+        <v>-1.8482</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0499</v>
+        <v>1.088</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0095</v>
+        <v>1.7217</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7874</v>
+        <v>-1.7684</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7634</v>
+        <v>-0.5538</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.0241</v>
+        <v>-1.2146</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4116</v>
+        <v>0.5276</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4758</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0643</v>
+        <v>0.5928</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7731</v>
+        <v>-2.2149</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.719</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7731</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8146</v>
+        <v>-3.3686</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4022</v>
+        <v>-1.2</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4124</v>
+        <v>-2.1687</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0812</v>
@@ -2248,13 +2248,13 @@
         <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7417</v>
+        <v>-0.2957</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5447</v>
+        <v>-0.3425</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.197</v>
+        <v>0.0467</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7731</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.5788</v>
+        <v>2.252899999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>8.422400000000001</v>
+        <v>8.422600000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.8437</v>
+        <v>-6.1698</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4888000000000006</v>
+        <v>-0.4887999999999999</v>
       </c>
       <c r="H24" t="n">
         <v>13.6763</v>
@@ -2305,7 +2305,7 @@
         <v>16.1933</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004000000000000004</v>
+        <v>0.003999999999999782</v>
       </c>
       <c r="M24" t="n">
         <v>-16.686</v>
@@ -2326,13 +2326,13 @@
         <v>16.6041</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2336999999999998</v>
+        <v>0.4404</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.3373</v>
+        <v>-2.3374</v>
       </c>
       <c r="U24" t="n">
-        <v>2.1036</v>
+        <v>2.7777</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6056</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484375_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484375_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>1.3283</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>-0.8317</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0562</v>
+        <v>0.607</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5003</v>
+        <v>0.607</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4441</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1453</v>
+        <v>0.607</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6465</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7917</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7928</v>
+        <v>0.607</v>
       </c>
       <c r="K4" t="n">
-        <v>0.596</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1968</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6476</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2425</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4051</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3859</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3624</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0235</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0549</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0318</v>
+        <v>0.0562</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9728</v>
+        <v>0.5003</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9409</v>
+        <v>-0.4441</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4729</v>
+        <v>2.1453</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.6316</v>
+        <v>-0.6465</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1587</v>
+        <v>2.7917</v>
       </c>
       <c r="J5" t="n">
-        <v>1.803</v>
+        <v>3.7928</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2213</v>
+        <v>0.596</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0243</v>
+        <v>3.1968</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2759</v>
+        <v>-1.6476</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.4103</v>
+        <v>-1.2425</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1344</v>
+        <v>-0.4051</v>
       </c>
       <c r="P5" t="n">
-        <v>0.586</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.196</v>
+        <v>-0.3859</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2674</v>
+        <v>-0.3624</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4634</v>
+        <v>-0.0235</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2772</v>
+        <v>0.0549</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8865</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0577</v>
+        <v>0.0318</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2578</v>
+        <v>0.9728</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2002</v>
+        <v>-0.9409</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2575</v>
+        <v>-0.4729</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1765</v>
+        <v>-2.6316</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0809</v>
+        <v>2.1587</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2939</v>
+        <v>1.803</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3482</v>
+        <v>-0.2213</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0543</v>
+        <v>2.0243</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9636</v>
+        <v>-2.2759</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8283</v>
+        <v>-2.4103</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1352</v>
+        <v>0.1344</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3095</v>
+        <v>0.196</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0728</v>
+        <v>-0.2674</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3823</v>
+        <v>0.4634</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1089</v>
+        <v>-0.2772</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1089</v>
+        <v>0.6093</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1009</v>
+        <v>-0.0577</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5266</v>
+        <v>-0.2578</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.6274</v>
+        <v>0.2002</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9284</v>
+        <v>-2.2575</v>
       </c>
       <c r="H7" t="n">
-        <v>1.471</v>
+        <v>-2.1765</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4574</v>
+        <v>-0.0809</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4411</v>
+        <v>-1.2939</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5787</v>
+        <v>-1.3482</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8624</v>
+        <v>0.0543</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5127</v>
+        <v>-0.9636</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1077</v>
+        <v>-0.8283</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4051</v>
+        <v>-0.1352</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1231</v>
+        <v>0.3095</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1602</v>
+        <v>-0.0728</v>
       </c>
       <c r="U7" t="n">
-        <v>0.037</v>
+        <v>0.3823</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.1014</v>
+        <v>1.1089</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2224</v>
+        <v>1.1089</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.3238</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2422</v>
+        <v>-0.1009</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5788</v>
+        <v>3.5266</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.821</v>
+        <v>-3.6274</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2817</v>
+        <v>2.9284</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1747</v>
+        <v>1.471</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.107</v>
+        <v>1.4574</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5149</v>
+        <v>4.4411</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0261</v>
+        <v>2.5787</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5112</v>
+        <v>1.8624</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7966</v>
+        <v>-1.5127</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.2008</v>
+        <v>-1.1077</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4043</v>
+        <v>-0.4051</v>
       </c>
       <c r="P8" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1176</v>
+        <v>-0.1231</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1464</v>
+        <v>-0.1602</v>
       </c>
       <c r="U8" t="n">
-        <v>0.264</v>
+        <v>0.037</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6642</v>
+        <v>-3.1014</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3824</v>
+        <v>0.2224</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.0466</v>
+        <v>-3.3238</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3479</v>
+        <v>-0.2422</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3434</v>
+        <v>2.5788</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0045</v>
+        <v>-2.821</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4889</v>
+        <v>-0.2817</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9877</v>
+        <v>-0.1747</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4988</v>
+        <v>-0.107</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2378</v>
+        <v>1.5149</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1433</v>
+        <v>2.0261</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0945</v>
+        <v>-0.5112</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7267</v>
+        <v>-1.7966</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.131</v>
+        <v>-2.2008</v>
       </c>
       <c r="O9" t="n">
         <v>0.4043</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0544</v>
+        <v>0.1176</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4092</v>
+        <v>-0.1464</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3548</v>
+        <v>0.264</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.3824</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-3.0466</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7953</v>
+        <v>-0.3479</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0738</v>
+        <v>-0.3434</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7215</v>
+        <v>-0.0045</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9416</v>
+        <v>-0.4889</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4807</v>
+        <v>-1.9877</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5391</v>
+        <v>1.4988</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0968</v>
+        <v>1.2378</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7125</v>
+        <v>0.1433</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8093</v>
+        <v>1.0945</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0384</v>
+        <v>-1.7267</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7682</v>
+        <v>-2.131</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2702</v>
+        <v>0.4043</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3811</v>
+        <v>-0.0544</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1939</v>
+        <v>-0.4092</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1872</v>
+        <v>0.3548</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2258</v>
+        <v>-2.4023</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4911</v>
+        <v>-1.6808</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7347</v>
+        <v>-0.7215</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2686</v>
+        <v>-1.5486</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7155</v>
+        <v>-1.4807</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5531</v>
+        <v>-0.0679</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1654</v>
+        <v>-0.5102</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6127</v>
+        <v>-0.7125</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5527</v>
+        <v>0.2023</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1032</v>
+        <v>-1.0384</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1028</v>
+        <v>-0.7682</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0004</v>
+        <v>-0.2702</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.1255</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
         <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.3811</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1334</v>
+        <v>-0.1939</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1416</v>
+        <v>-0.1872</v>
       </c>
       <c r="V11" t="n">
-        <v>2.16</v>
+        <v>-0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6709000000000009</v>
+        <v>-3.2258</v>
       </c>
       <c r="E12" t="n">
-        <v>8.028900000000002</v>
+        <v>-2.4911</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.699400000000001</v>
+        <v>-0.7347</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4889000000000001</v>
+        <v>-2.2686</v>
       </c>
       <c r="H12" t="n">
-        <v>-13.6761</v>
+        <v>-1.7155</v>
       </c>
       <c r="I12" t="n">
-        <v>14.1651</v>
+        <v>-0.5531</v>
       </c>
       <c r="J12" t="n">
-        <v>16.6861</v>
+        <v>-1.1654</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5171</v>
+        <v>-0.6127</v>
       </c>
       <c r="L12" t="n">
-        <v>14.1689</v>
+        <v>-0.5527</v>
       </c>
       <c r="M12" t="n">
-        <v>-16.1973</v>
+        <v>-1.1032</v>
       </c>
       <c r="N12" t="n">
-        <v>-16.1933</v>
+        <v>-1.1028</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.004000000000000103</v>
+        <v>-0.0004</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.907</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q12" t="n">
-        <v>-16.6043</v>
+        <v>-3.9069</v>
       </c>
       <c r="R12" t="n">
-        <v>12.6975</v>
+        <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1416</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1959</v>
+        <v>-0.1334</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3373</v>
+        <v>0.1416</v>
       </c>
       <c r="V12" t="n">
-        <v>1.6056</v>
+        <v>2.16</v>
       </c>
       <c r="W12" t="n">
-        <v>9.142700000000001</v>
+        <v>2.7145</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.5371</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>DM GROUP MOLLET</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4219</v>
+        <v>-0.6709000000000005</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0569</v>
+        <v>8.0289</v>
       </c>
       <c r="F13" t="n">
-        <v>1.365</v>
+        <v>-8.699399999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>2.0677</v>
+        <v>0.4888999999999997</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1926</v>
+        <v>-13.6761</v>
       </c>
       <c r="I13" t="n">
-        <v>1.875</v>
+        <v>14.1651</v>
       </c>
       <c r="J13" t="n">
-        <v>2.213</v>
+        <v>16.6861</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2021</v>
+        <v>2.5171</v>
       </c>
       <c r="L13" t="n">
-        <v>2.4151</v>
+        <v>14.1689</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1453</v>
+        <v>-16.1973</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3948</v>
+        <v>-16.1933</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5401</v>
+        <v>-0.004000000000000048</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5627</v>
+        <v>-3.907</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-16.6043</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>12.6975</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3137</v>
+        <v>1.1416</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2613</v>
+        <v>-1.1959</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0524</v>
+        <v>2.3373</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1052</v>
+        <v>1.6056</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1052</v>
+        <v>9.142700000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
-      </c>
+        <v>-7.5371</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3717</v>
+        <v>5.4219</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6401</v>
+        <v>4.0569</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2684</v>
+        <v>1.365</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7967</v>
+        <v>2.0677</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9688</v>
+        <v>0.1926</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.1721</v>
+        <v>1.875</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9699</v>
+        <v>2.213</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8485</v>
+        <v>-0.2021</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1214</v>
+        <v>2.4151</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1733</v>
+        <v>-0.1453</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1203</v>
+        <v>0.3948</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.2935</v>
+        <v>-0.5401</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4615</v>
+        <v>-0.3137</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3929</v>
+        <v>-0.2613</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0687</v>
+        <v>-0.0524</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9414</v>
+        <v>2.1052</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2772</v>
+        <v>2.1052</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2639</v>
+        <v>3.3717</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1526</v>
+        <v>3.6401</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8887</v>
+        <v>-0.2684</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1689</v>
+        <v>0.7967</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8821</v>
+        <v>2.9688</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7132</v>
+        <v>-2.1721</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5517</v>
+        <v>2.9699</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6454</v>
+        <v>2.8485</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.1214</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3828</v>
+        <v>-2.1733</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7634</v>
+        <v>0.1203</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6194</v>
+        <v>-2.2935</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>0.095</v>
+        <v>0.4615</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6643</v>
+        <v>0.3929</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7592</v>
+        <v>0.0687</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1728,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8797</v>
+        <v>0.9569</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2127</v>
+        <v>1.8456</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.333</v>
+        <v>-0.8887</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.4054</v>
+        <v>0.8619</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3848</v>
+        <v>2.5751</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.7902</v>
+        <v>-1.7132</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4661</v>
+        <v>3.2447</v>
       </c>
       <c r="K16" t="n">
-        <v>3.153</v>
+        <v>3.3385</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6869</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.8714</v>
+        <v>-2.3828</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7682</v>
+        <v>-0.7634</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.1032</v>
+        <v>-1.6194</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1702,28 +1773,33 @@
         <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.207</v>
+        <v>0.095</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6237</v>
+        <v>-0.6643</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4167</v>
+        <v>0.7592</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4921</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.3238</v>
+        <v>1.2186</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8317</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3993</v>
+        <v>0.8797</v>
       </c>
       <c r="E17" t="n">
-        <v>0.797</v>
+        <v>3.2127</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3977</v>
+        <v>-2.333</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1063</v>
+        <v>-1.4054</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7403999999999999</v>
+        <v>2.3848</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.634</v>
+        <v>-3.7902</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7158</v>
+        <v>2.4661</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6754</v>
+        <v>3.153</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>-0.6869</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6095</v>
+        <v>-3.8714</v>
       </c>
       <c r="N17" t="n">
-        <v>0.065</v>
+        <v>-0.7682</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6745</v>
+        <v>-3.1032</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0977</v>
+        <v>-0.207</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.6237</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1789</v>
+        <v>0.4167</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.4921</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.3238</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PLANELL IGLESIAS</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.313</v>
+        <v>0.3993</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1626</v>
+        <v>0.797</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4756</v>
+        <v>-0.3977</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4768</v>
+        <v>0.1063</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0703</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5936</v>
+        <v>-0.634</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3521</v>
+        <v>0.7158</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9452</v>
+        <v>0.6754</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1247</v>
+        <v>-0.6095</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1251</v>
+        <v>0.065</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0004</v>
+        <v>-0.6745</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2036</v>
+        <v>-0.0977</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1939</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3975</v>
+        <v>-0.1789</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>A. PLANELL IGLESIAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0979</v>
+        <v>0.313</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2818</v>
+        <v>-2.1626</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3797</v>
+        <v>2.4756</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6825</v>
+        <v>0.4768</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3953</v>
+        <v>1.0703</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0778</v>
+        <v>-0.5936</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2308</v>
+        <v>0.3521</v>
       </c>
       <c r="K19" t="n">
-        <v>1.824</v>
+        <v>0.9452</v>
       </c>
       <c r="L19" t="n">
         <v>-0.5931999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9133</v>
+        <v>0.1247</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4287</v>
+        <v>0.1251</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4846</v>
+        <v>-0.0004</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
         <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3357</v>
+        <v>0.2036</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.004</v>
+        <v>-0.1939</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3397</v>
+        <v>0.3975</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4448</v>
+        <v>0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4448</v>
+        <v>0.6093</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2752</v>
+        <v>0.307</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7401</v>
+        <v>0.307</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5351</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4818</v>
+        <v>0.307</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4009</v>
+        <v>0.307</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4174</v>
+        <v>0.307</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2034</v>
+        <v>0.307</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6208</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0644</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6042999999999999</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5399</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1011</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1808</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07969999999999999</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2877</v>
+        <v>0.0979</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5974</v>
+        <v>-0.2818</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8851</v>
+        <v>0.3797</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7375</v>
+        <v>-0.6825</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2461</v>
+        <v>1.3953</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9836</v>
+        <v>-2.0778</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0499</v>
+        <v>1.2308</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0095</v>
+        <v>1.824</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0405</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7874</v>
+        <v>-1.9133</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7634</v>
+        <v>-0.4287</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0241</v>
+        <v>-1.4846</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1678</v>
+        <v>0.3357</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4758</v>
+        <v>-0.004</v>
       </c>
       <c r="U21" t="n">
-        <v>0.308</v>
+        <v>0.3397</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.7731</v>
+        <v>0.4448</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.4448</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.563</v>
+        <v>-1.2752</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6496</v>
+        <v>-0.7401</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9134</v>
+        <v>-0.5351</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6804</v>
+        <v>0.4818</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1678</v>
+        <v>0.4009</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8482</v>
+        <v>0.0809</v>
       </c>
       <c r="J22" t="n">
-        <v>1.088</v>
+        <v>0.4174</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7217</v>
+        <v>-0.2034</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.6208</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7684</v>
+        <v>0.0644</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5538</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2146</v>
+        <v>-0.5399</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
         <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5276</v>
+        <v>-0.1011</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.1808</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5928</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.2149</v>
+        <v>-2.4373</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.719</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4959</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3686</v>
+        <v>-2.2877</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2</v>
+        <v>0.5974</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1687</v>
+        <v>-2.8851</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0812</v>
+        <v>-0.7375</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7728</v>
+        <v>1.2461</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3083</v>
+        <v>-1.9836</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8575</v>
+        <v>2.0499</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2239</v>
+        <v>2.0095</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2237</v>
+        <v>-2.7874</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.549</v>
+        <v>-0.7634</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6747</v>
+        <v>-2.0241</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2957</v>
+        <v>-0.1678</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3425</v>
+        <v>-0.4758</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0467</v>
+        <v>0.308</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7731</v>
@@ -2264,12 +2370,17 @@
       </c>
       <c r="X23" t="n">
         <v>-1.7731</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-2.563</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.6496</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.9134</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.6804</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.1678</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.8482</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.7217</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.7684</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.5538</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.2146</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.5276</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.06519999999999999</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-2.2149</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.719</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.3686</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-2.1687</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.0812</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.7728</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.3083</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.8575</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.2239</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.2237</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.549</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.6747</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.2957</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.3425</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.7731</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.7731</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484375_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>2.252899999999999</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>8.422600000000001</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>-6.1698</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>-0.4887999999999999</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H26" t="n">
         <v>13.6763</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I26" t="n">
         <v>-14.1651</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J26" t="n">
         <v>16.1972</v>
       </c>
-      <c r="K24" t="n">
-        <v>16.1933</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K26" t="n">
+        <v>16.1934</v>
+      </c>
+      <c r="L26" t="n">
         <v>0.003999999999999782</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>-16.686</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>-2.517</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O26" t="n">
         <v>-14.169</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>3.907</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-12.6971</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>16.6041</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>0.4404</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>-2.3374</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>2.7777</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>-1.6056</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>7.259899999999999</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-8.865499999999999</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
